--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1,314 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12900"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24045" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>item.EQuality</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>最差品质</t>
-  </si>
-  <si>
-    <t>BLUE</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>PURPLE</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>紫色的</t>
-  </si>
-  <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>test.AccessFlag</t>
-  </si>
-  <si>
-    <t>WRITE</t>
-  </si>
-  <si>
-    <t>READ</t>
-  </si>
-  <si>
-    <t>TRUNCATE</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>READ_WRITE</t>
-  </si>
-  <si>
-    <t>WRITE|READ</t>
-  </si>
-  <si>
-    <t>位标记使用示例</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -506,7 +376,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -627,169 +497,216 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -843,11 +760,74 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1107,231 +1087,783 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.8761904761905" customWidth="1"/>
-    <col min="4" max="5" width="14.1238095238095" customWidth="1"/>
-    <col min="6" max="6" width="9.37142857142857" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5047619047619" customWidth="1"/>
-    <col min="9" max="9" width="5.24761904761905" customWidth="1"/>
-    <col min="10" max="10" width="12.1238095238095" customWidth="1"/>
-    <col min="11" max="11" width="15.1238095238095" customWidth="1"/>
+    <col width="19" customWidth="1" style="4" min="2" max="2"/>
+    <col width="20.8761904761905" customWidth="1" style="4" min="3" max="3"/>
+    <col width="14.1238095238095" customWidth="1" style="4" min="4" max="5"/>
+    <col width="9.37142857142857" customWidth="1" style="4" min="6" max="6"/>
+    <col width="5" customWidth="1" style="4" min="7" max="7"/>
+    <col width="13.5047619047619" customWidth="1" style="4" min="8" max="8"/>
+    <col width="5.24761904761905" customWidth="1" style="4" min="9" max="9"/>
+    <col width="12.1238095238095" customWidth="1" style="4" min="10" max="10"/>
+    <col width="15.1238095238095" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" s="4">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>item.EQuality</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>最差品质</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>BLUE</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>蓝色的</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>PURPLE</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>紫色的</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>红</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>最高品质</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>test.AccessFlag</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>WRITE</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>TRUNCATE</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>READ_WRITE</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>WRITE|READ</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>位标记使用示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>fp.ERoute</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>原型路线</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="0" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>Devour</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>吞噬扩张型</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="0" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>Specialist</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>功能特化型</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="0" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>科技统治型</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="0" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>fp.EFormId</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>玩家形态</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>细胞</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="0" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>Creature</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="0" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>fp.EMicroChoice</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>细胞微选择</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="0" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>Gluttony</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>贪食囊</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>Phototaxis</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>趋光纤毛</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="0" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>Metabolic</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>代谢泡</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="0" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>fp.EModuleId</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>构筑模块</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="0" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>Maw</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>吞噬口器</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="0" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>ThickWall</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>厚壁细胞层</t>
+        </is>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" s="0" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>Cilia</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>感知纤毛</t>
+        </is>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="0" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>Nerve</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>协同神经束</t>
+        </is>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" s="0" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>Zap</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>原始放电囊</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="K28" s="0" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>Conduit</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>能量导流组织</t>
+        </is>
+      </c>
+      <c r="J29" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="K29" s="0" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>fp.EFoodId</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="b">
+      <c r="D30" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>食物类型</t>
+        </is>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>A型食物</t>
+        </is>
+      </c>
+      <c r="J30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" s="0" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>B型食物</t>
+        </is>
+      </c>
+      <c r="J31" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="0" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fp.EEnemyId</t>
+        </is>
+      </c>
+      <c r="C32" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D32" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>敌人类型</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Threat</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>细胞威胁</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="8:11">
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5">
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Herbivore</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>草食虫</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11">
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6">
+      <c r="K33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Predator</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>掠食虫</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11">
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7">
+      <c r="K34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="8:10">
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="8:10">
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="8:10">
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="8:11">
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" t="s">
-        <v>39</v>
-      </c>
+      <c r="K35" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L35"/>
+  <dimension ref="A1:L212"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -1780,84 +1780,3392 @@
       <c r="K31" s="0" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>fp.EEnemyId</t>
         </is>
       </c>
-      <c r="C32" t="b">
+      <c r="C32" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D32" t="b">
+      <c r="D32" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>敌人类型</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="0" t="inlineStr">
         <is>
           <t>Threat</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="0" t="inlineStr">
         <is>
           <t>细胞威胁</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" s="0" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="0" t="inlineStr">
         <is>
           <t>Herbivore</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="0" t="inlineStr">
         <is>
           <t>草食虫</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" s="0" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="0" t="inlineStr">
         <is>
           <t>Predator</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="0" t="inlineStr">
         <is>
           <t>掠食虫</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J34" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" s="0" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="0" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="0" t="inlineStr">
         <is>
           <t>精英</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="J35" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" s="0" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>cell.ERoute</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>原型路线</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Devour</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>吞噬扩张</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Agile</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>机动猎食</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>电化统治</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Spore</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>孢子繁殖</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Nest</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>菌毯筑巢</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Corrupt</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>异化污染</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>6</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>跨路线联动</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>cell.ERarity</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>卡牌稀有度</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>建立基础循环</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>形成路线联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>2</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>改变一条路线的运作方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Aberrant</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>异化</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>3</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>强机制变化 + 明确副作用</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>原核遗产</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>定义整局策略</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>cell.ETrigger</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>卡牌触发时机</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>获得即生效</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>OnDevour</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>吞噬时</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>击杀时</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>命中时</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>3</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>OnHurt</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>受伤时</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>OnDash</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>冲刺时</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>OnAbilityCast</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>施放技能时</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>6</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>OnLevelUp</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>升级时</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>7</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>OnLowHealth</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>低血时</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>OnPhaseStart</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>时期开始时</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>9</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>OnTick</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>周期性</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>10</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>OnVolumeChanged</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>体积变化时</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>11</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>OnEcoEvent</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>生态事件时</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>12</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>cell.EEffectKind</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>效果类别</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>伤害</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Spawn</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>生成单位</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>3</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>属性修正</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>4</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Resource</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>资源变化</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Dash</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>位移</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>6</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>投射物</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>7</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>持续区域</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>8</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>改规则</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>9</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>cell.EEffectShape</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>效果形状</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>圆形</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Cone</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>锥形</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>2</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>直线</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>3</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>单目标</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>4</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>指定点</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>5</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>cell.EAffix</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>词缀</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Proliferate</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>增殖</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>生成数量翻倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Conductive</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>导电</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>2</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>与电系联动</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Corrosive</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>腐蚀</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>3</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>持续削弱体积护壳速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Refund</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>回流</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>4</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>返还体力冷却营养</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Fission</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>裂变</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>5</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>结束时生成次级效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Mimic</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>拟态</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>6</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>复制上次触发的弱版</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Hunger</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>饥饿</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>7</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>低资源时更强</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Homeostasis</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>稳态</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>8</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>静止筑巢时更强</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Overload</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>过载</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>9</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>强化但自损</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Symbiosis</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>共生</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>10</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>附属体越多本体越强</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>贯穿</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>11</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>效果穿透目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Ricochet</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>弹射</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>12</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>命中后跳向下一目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Lingering</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>滞留</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>13</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>留下持续区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>引力</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>14</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>拉拽附近目标</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Fear</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>恐惧</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>15</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>逼退小型敌人</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>标记</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>16</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>施加易伤标记</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Parasite</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>寄生</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>17</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>附着并持续削弱</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Siphon</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>虹吸</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>18</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>转化敌方资源</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Harden</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>硬化</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>19</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>提高受击阈值</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Molt</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>蜕变</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>20</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>受击时转换形态</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>连锁</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>21</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>触发次数递增</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Resonate</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>共振</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>22</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>多目标互相加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Delayed</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>淤积</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>23</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>效果延迟但加倍</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Catalyze</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>催化</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>24</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>缩短其他冷却</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>分食</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>25</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>大目标死亡裂成小块</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Hatch</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>孵化</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>26</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>延迟生成友方单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Crystallize</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>晶化</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>27</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>累积破碎层数</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Tidal</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>潮汐</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>28</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>周期性强弱交替</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>BoneEater</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>噬骨</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>29</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>对高体积目标增伤</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Detached</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>游离</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>30</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>效果可脱离本体存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Entropy</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>逆熵</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>31</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>消耗污染度换取回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sacrifice</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>献祭</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>32</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>消耗自身资源大幅强化</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>cell.ERuleFlag</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>规则开关</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>CorpseEdible</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>尸体可食</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>1</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>FailedDevourCorrodes</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>吞噬失败致腐蚀</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>ComboNeverResets</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>连吃不清空</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>3</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>DashPierces</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>冲刺穿体</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>4</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>DashLeavesCurrent</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>冲刺留电流</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>5</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>CorpseConducts</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>尸体导电</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>6</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>MyceliumBoostsDevour</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>菌毯增益吞噬</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>7</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>AutoEscapeOnLowHp</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>濒死脱战</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>8</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>PollutionBecomesOverlord</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>污染满转霸主</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>9</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>MinionsFocusMarked</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>附属体集火标记</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>10</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>LargeTargetsSplit</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>大目标裂解</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>11</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>ExecuteCausesFear</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>处决致恐惧</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>12</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>cell.ETargetMode</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>技能瞄准方式</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>MoveDirection</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>移动方向</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>鼠标方向</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>2</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>NearestEnemy</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>最近敌人</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>MarkedEnemy</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>已标记敌人</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>4</v>
+      </c>
+      <c r="K128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>cell.EStatId</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>属性 id</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>MaxHealth</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>最大生命</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>移速</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>2</v>
+      </c>
+      <c r="K131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>体积</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>3</v>
+      </c>
+      <c r="K132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>MeleeDamage</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>近战伤害</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>4</v>
+      </c>
+      <c r="K133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>DevourRatio</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>吞噬门槛</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>5</v>
+      </c>
+      <c r="K134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>DevourGain</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>吞噬收益</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>6</v>
+      </c>
+      <c r="K135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>StaminaMax</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>体力上限</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>7</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>StaminaRegen</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>体力回复</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>8</v>
+      </c>
+      <c r="K137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>DashCost</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>冲刺消耗</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>9</v>
+      </c>
+      <c r="K138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>DashDistance</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>冲刺距离</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>10</v>
+      </c>
+      <c r="K139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>DashInvulnTime</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>冲刺无敌时长</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>11</v>
+      </c>
+      <c r="K140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>CooldownReduction</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>冷却缩减</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>12</v>
+      </c>
+      <c r="K141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>AreaScale</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>范围倍率</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>13</v>
+      </c>
+      <c r="K142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>AbilityPower</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>技能强度</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>14</v>
+      </c>
+      <c r="K143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>ElectricPower</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>电系强度</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>15</v>
+      </c>
+      <c r="K144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>ChainBonus</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>连锁加成</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>16</v>
+      </c>
+      <c r="K145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>MinionCap</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>附属体上限</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>17</v>
+      </c>
+      <c r="K146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>MinionPower</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>附属体强度</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>18</v>
+      </c>
+      <c r="K147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>HealthRegen</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>生命回复</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>19</v>
+      </c>
+      <c r="K148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>KillHeal</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>击杀回复</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>20</v>
+      </c>
+      <c r="K149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>DamageTaken</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>受伤倍率</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>21</v>
+      </c>
+      <c r="K150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>AggroScale</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>仇恨倍率</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>22</v>
+      </c>
+      <c r="K151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>PickupRadius</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>拾取半径</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>23</v>
+      </c>
+      <c r="K152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>EvoGain</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>进化能收益</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>24</v>
+      </c>
+      <c r="K153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>NutrientGain</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>营养质收益</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>25</v>
+      </c>
+      <c r="K154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>AbilitySlots</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>技能槽位</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>26</v>
+      </c>
+      <c r="K155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>PollutionCap</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>污染度上限</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>27</v>
+      </c>
+      <c r="K156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>MyceliumScale</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>菌毯范围</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>28</v>
+      </c>
+      <c r="K157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>ProjectileCount</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>投射物数量</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>29</v>
+      </c>
+      <c r="K158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>StatusDuration</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>状态时长</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>30</v>
+      </c>
+      <c r="K159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>cell.EModifierOp</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>修正器叠加层级</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>加值</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>PctAdd</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>加法百分比</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>同类相加</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>PctMul</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>乘法百分比</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>2</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>独立相乘</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>cell.EResourceKind</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>资源种类</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>生命值</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>1</v>
+      </c>
+      <c r="K164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Nutrient</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>营养质</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>2</v>
+      </c>
+      <c r="K165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Mutagen</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>突变质</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>EvoEnergy</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>进化能</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>4</v>
+      </c>
+      <c r="K167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Pollution</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>污染度</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>5</v>
+      </c>
+      <c r="K168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>体积</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>6</v>
+      </c>
+      <c r="K169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Stamina</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>体力</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>7</v>
+      </c>
+      <c r="K170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>cell.EDraftKind</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>选卡类型</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>常规升级</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>3 选 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>精英进化</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>4 选 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Corrupt</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>污染进化</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>2</v>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>3 选 1 带代价</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Repair</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>修复进化</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>2 选 1 保底</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Legacy</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>遗产进化</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>4</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>3 选 1 遗产卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>cell.EBehaviorKind</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>行为原型</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Stationary</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>固守</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Drift</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>漂浮</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Chase</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>追猎</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>2</v>
+      </c>
+      <c r="K178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Patrol</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>巡逻</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Charge</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>冲撞</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>4</v>
+      </c>
+      <c r="K180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Ranged</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>远程</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>5</v>
+      </c>
+      <c r="K181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Swarm</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>群体</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>6</v>
+      </c>
+      <c r="K182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Flee</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>逃逸</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>7</v>
+      </c>
+      <c r="K183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Orbit</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>环绕</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>8</v>
+      </c>
+      <c r="K184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Latch</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>附着</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>9</v>
+      </c>
+      <c r="K185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>cell.EStatus</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>状态位</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Conductive</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>导电</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>1</v>
+      </c>
+      <c r="K187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Breached</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>破体</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>2</v>
+      </c>
+      <c r="K188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Marked</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>标记</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>4</v>
+      </c>
+      <c r="K189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Slowed</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>减速</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>8</v>
+      </c>
+      <c r="K190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Stunned</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>麻痹</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>16</v>
+      </c>
+      <c r="K191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Corroded</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>腐蚀</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>32</v>
+      </c>
+      <c r="K192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Feared</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>恐惧</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>64</v>
+      </c>
+      <c r="K193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Parasited</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>寄生</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>128</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Invulnerable</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>无敌</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>256</v>
+      </c>
+      <c r="K195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Hardened</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>硬化</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>512</v>
+      </c>
+      <c r="K196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Crystallized</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>晶化</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Infected</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>感染</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>2048</v>
+      </c>
+      <c r="K198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Vulnerable</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>易伤</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>4096</v>
+      </c>
+      <c r="K199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Burning</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>燃烧</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>8192</v>
+      </c>
+      <c r="K200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Polluted</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>污染</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>16384</v>
+      </c>
+      <c r="K201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Pulled</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>被拉拽</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>32768</v>
+      </c>
+      <c r="K202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Unedible</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>不可吞噬</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>65536</v>
+      </c>
+      <c r="K203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>131072</v>
+      </c>
+      <c r="K204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>首领</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>262144</v>
+      </c>
+      <c r="K205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>OnMycelium</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>菌毯上</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>524288</v>
+      </c>
+      <c r="K206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>cell.EFaction</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>阵营</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>玩家</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>PlayerMinion</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>玩家附属体</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>2</v>
+      </c>
+      <c r="K209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Hostile</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>敌对</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>中立</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>4</v>
+      </c>
+      <c r="K211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Pickup</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>拾取物</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>5</v>
+      </c>
+      <c r="K212" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L212"/>
+  <dimension ref="A1:L215"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -5167,6 +5167,74 @@
       </c>
       <c r="K212" t="inlineStr"/>
     </row>
+    <row r="213">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>cell.EContentKind</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>内容种类（代谢化迁移）</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Organelle</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>器官</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>基因</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>2</v>
+      </c>
+      <c r="K215" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L215"/>
+  <dimension ref="A1:L217"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -4696,544 +4696,584 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>cell.EStatus</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>状态位</t>
-        </is>
-      </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>MinionSeekAttack</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>索敌近战</t>
         </is>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
-      </c>
-      <c r="K186" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>玩家召唤物专用：索敌最近敌对目标，进入 attackRange 后周期造成 attackDamage</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="H187" t="inlineStr">
         <is>
-          <t>Conductive</t>
+          <t>MinionSeekExplode</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>导电</t>
+          <t>索敌自爆</t>
         </is>
       </c>
       <c r="J187" t="n">
-        <v>1</v>
-      </c>
-      <c r="K187" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>玩家召唤物专用：索敌最近敌对目标，进入 attackRange 后以 preferredRange 为半径 AOE 自爆并消亡</t>
+        </is>
+      </c>
     </row>
     <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>cell.EStatus</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>状态位</t>
+        </is>
+      </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Breached</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>破体</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="H189" t="inlineStr">
         <is>
-          <t>Marked</t>
+          <t>Conductive</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>标记</t>
+          <t>导电</t>
         </is>
       </c>
       <c r="J189" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="H190" t="inlineStr">
         <is>
-          <t>Slowed</t>
+          <t>Breached</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>减速</t>
+          <t>破体</t>
         </is>
       </c>
       <c r="J190" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="H191" t="inlineStr">
         <is>
-          <t>Stunned</t>
+          <t>Marked</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>麻痹</t>
+          <t>标记</t>
         </is>
       </c>
       <c r="J191" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="H192" t="inlineStr">
         <is>
-          <t>Corroded</t>
+          <t>Slowed</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>腐蚀</t>
+          <t>减速</t>
         </is>
       </c>
       <c r="J192" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="H193" t="inlineStr">
         <is>
-          <t>Feared</t>
+          <t>Stunned</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>恐惧</t>
+          <t>麻痹</t>
         </is>
       </c>
       <c r="J193" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="H194" t="inlineStr">
         <is>
-          <t>Parasited</t>
+          <t>Corroded</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>寄生</t>
+          <t>腐蚀</t>
         </is>
       </c>
       <c r="J194" t="n">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="H195" t="inlineStr">
         <is>
-          <t>Invulnerable</t>
+          <t>Feared</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>无敌</t>
+          <t>恐惧</t>
         </is>
       </c>
       <c r="J195" t="n">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="H196" t="inlineStr">
         <is>
-          <t>Hardened</t>
+          <t>Parasited</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>硬化</t>
+          <t>寄生</t>
         </is>
       </c>
       <c r="J196" t="n">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="H197" t="inlineStr">
         <is>
-          <t>Crystallized</t>
+          <t>Invulnerable</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>晶化</t>
+          <t>无敌</t>
         </is>
       </c>
       <c r="J197" t="n">
-        <v>1024</v>
+        <v>256</v>
       </c>
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="H198" t="inlineStr">
         <is>
-          <t>Infected</t>
+          <t>Hardened</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>感染</t>
+          <t>硬化</t>
         </is>
       </c>
       <c r="J198" t="n">
-        <v>2048</v>
+        <v>512</v>
       </c>
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="H199" t="inlineStr">
         <is>
-          <t>Vulnerable</t>
+          <t>Crystallized</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>易伤</t>
+          <t>晶化</t>
         </is>
       </c>
       <c r="J199" t="n">
-        <v>4096</v>
+        <v>1024</v>
       </c>
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="H200" t="inlineStr">
         <is>
-          <t>Burning</t>
+          <t>Infected</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>燃烧</t>
+          <t>感染</t>
         </is>
       </c>
       <c r="J200" t="n">
-        <v>8192</v>
+        <v>2048</v>
       </c>
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="H201" t="inlineStr">
         <is>
-          <t>Polluted</t>
+          <t>Vulnerable</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>污染</t>
+          <t>易伤</t>
         </is>
       </c>
       <c r="J201" t="n">
-        <v>16384</v>
+        <v>4096</v>
       </c>
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="H202" t="inlineStr">
         <is>
-          <t>Pulled</t>
+          <t>Burning</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>被拉拽</t>
+          <t>燃烧</t>
         </is>
       </c>
       <c r="J202" t="n">
-        <v>32768</v>
+        <v>8192</v>
       </c>
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="H203" t="inlineStr">
         <is>
-          <t>Unedible</t>
+          <t>Polluted</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>不可吞噬</t>
+          <t>污染</t>
         </is>
       </c>
       <c r="J203" t="n">
-        <v>65536</v>
+        <v>16384</v>
       </c>
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="H204" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Pulled</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>精英</t>
+          <t>被拉拽</t>
         </is>
       </c>
       <c r="J204" t="n">
-        <v>131072</v>
+        <v>32768</v>
       </c>
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="H205" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Unedible</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>首领</t>
+          <t>不可吞噬</t>
         </is>
       </c>
       <c r="J205" t="n">
-        <v>262144</v>
+        <v>65536</v>
       </c>
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="H206" t="inlineStr">
         <is>
-          <t>OnMycelium</t>
+          <t>Elite</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>菌毯上</t>
+          <t>精英</t>
         </is>
       </c>
       <c r="J206" t="n">
-        <v>524288</v>
+        <v>131072</v>
       </c>
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>cell.EFaction</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>阵营</t>
-        </is>
-      </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>首领</t>
         </is>
       </c>
       <c r="J207" t="n">
-        <v>0</v>
+        <v>262144</v>
       </c>
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="H208" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>OnMycelium</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>玩家</t>
+          <t>菌毯上</t>
         </is>
       </c>
       <c r="J208" t="n">
-        <v>1</v>
+        <v>524288</v>
       </c>
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>cell.EFaction</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>阵营</t>
+        </is>
+      </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>PlayerMinion</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>玩家附属体</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="H210" t="inlineStr">
         <is>
-          <t>Hostile</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>敌对</t>
+          <t>玩家</t>
         </is>
       </c>
       <c r="J210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="H211" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>PlayerMinion</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>中立</t>
+          <t>玩家附属体</t>
         </is>
       </c>
       <c r="J211" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="H212" t="inlineStr">
         <is>
-          <t>Pickup</t>
+          <t>Hostile</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>拾取物</t>
+          <t>敌对</t>
         </is>
       </c>
       <c r="J212" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>cell.EContentKind</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>内容种类（代谢化迁移）</t>
-        </is>
-      </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>中立</t>
         </is>
       </c>
       <c r="J213" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="H214" t="inlineStr">
         <is>
+          <t>Pickup</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>拾取物</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>5</v>
+      </c>
+      <c r="K214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>cell.EContentKind</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>内容种类（代谢化迁移）</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="H216" t="inlineStr">
+        <is>
           <t>Organelle</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
+      <c r="I216" t="inlineStr">
         <is>
           <t>器官</t>
         </is>
       </c>
-      <c r="J214" t="n">
+      <c r="J216" t="n">
         <v>1</v>
       </c>
-      <c r="K214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="H215" t="inlineStr">
+      <c r="K216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="H217" t="inlineStr">
         <is>
           <t>Gene</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
+      <c r="I217" t="inlineStr">
         <is>
           <t>基因</t>
         </is>
       </c>
-      <c r="J215" t="n">
+      <c r="J217" t="n">
         <v>2</v>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L217"/>
+  <dimension ref="A1:L218"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -5275,6 +5275,22 @@
       </c>
       <c r="K217" t="inlineStr"/>
     </row>
+    <row r="218">
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Structural</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>结构器官</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>3</v>
+      </c>
+      <c r="K218" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
